--- a/blanks/aromaderm-1000.xlsx
+++ b/blanks/aromaderm-1000.xlsx
@@ -11,7 +11,7 @@
     <sheet name="AROMADERM" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="Excel_BuiltIn__FilterDatabase" vbProcedure="false">AROMADERM!$A$5:$E$49</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">AROMADERM!$A$6:$E$28</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -1145,6 +1145,7 @@
       <c r="E28" s="35"/>
     </row>
   </sheetData>
+  <autoFilter ref="A6:E28"/>
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" display="profi@styx-naturcosmetic.ru"/>
   </hyperlinks>
